--- a/exports/peak_candidates.xlsx
+++ b/exports/peak_candidates.xlsx
@@ -3482,14 +3482,14 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I35" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>3503.251</v>
@@ -3503,15 +3503,15 @@
         <v>0</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3339.202</v>
+        <v>3293.468</v>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>2025Q2-2026Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.953</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="3" t="n">
@@ -3531,11 +3531,7 @@
           <t>glp1_receptor_agonist</t>
         </is>
       </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+      <c r="W35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">

--- a/exports/peak_candidates.xlsx
+++ b/exports/peak_candidates.xlsx
@@ -17250,7 +17250,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Warner-Lambert</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1998Q1</t>
+          <t>1997Q1</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -17282,7 +17282,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>13137</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2009Q4</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -17867,7 +17867,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>7642.36</v>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2009Q4</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -17950,7 +17950,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>7310.258</v>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2009Q4</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -18033,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>7240.126</v>
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2015Q2</t>
+          <t>2009Q1</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -21974,7 +21974,7 @@
         <v>1</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>2269</v>
@@ -24923,7 +24923,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2009Q4</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -24935,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>1450.686</v>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2016Q2</t>
+          <t>2016Q1</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
@@ -28398,7 +28398,7 @@
         <v>1</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K141" s="4" t="n">
         <v>655</v>

--- a/exports/peak_candidates.xlsx
+++ b/exports/peak_candidates.xlsx
@@ -18519,7 +18519,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2017Q2</t>
+          <t>2016Q2</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -18531,7 +18531,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>6502.747</v>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2002Q3</t>
+          <t>2001Q1</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -23496,7 +23496,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>1701.992</v>
@@ -23624,7 +23624,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Odefsey</t>
+          <t>Betaseron</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -23634,12 +23634,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Schering AG</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -23654,60 +23654,64 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2016Q3</t>
+          <t>2000Q4</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="I85" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1672</v>
+        <v>1690.883</v>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>2020Q1-2020Q4</t>
+          <t>2009Q1-2009Q4</t>
         </is>
       </c>
       <c r="M85" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>1047</v>
+        <v>207.558</v>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q1-2024Q4</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.626</v>
+        <v>0.123</v>
       </c>
       <c r="Q85" s="4" t="n"/>
       <c r="R85" s="3" t="n"/>
       <c r="S85" s="3" t="n"/>
       <c r="T85" s="3" t="n"/>
       <c r="U85" s="3" t="n">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="V85" s="3" t="inlineStr">
         <is>
-          <t>hiv_antiretroviral</t>
-        </is>
-      </c>
-      <c r="W85" s="3" t="n"/>
+          <t>interferon_beta</t>
+        </is>
+      </c>
+      <c r="W85" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Zepatier</t>
+          <t>Odefsey</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -23717,12 +23721,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -23737,41 +23741,41 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2016Q1</t>
+          <t>2016Q3</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I86" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1659</v>
+        <v>1672</v>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2017Q1-2017Q4</t>
+          <t>2020Q1-2020Q4</t>
         </is>
       </c>
       <c r="M86" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>167</v>
+        <v>1047</v>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>2020Q1-2020Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.101</v>
+        <v>0.626</v>
       </c>
       <c r="Q86" s="4" t="n"/>
       <c r="R86" s="3" t="n"/>
@@ -23782,19 +23786,15 @@
       </c>
       <c r="V86" s="3" t="inlineStr">
         <is>
-          <t>hcv_ns5a_protease_combination</t>
-        </is>
-      </c>
-      <c r="W86" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>hiv_antiretroviral</t>
+        </is>
+      </c>
+      <c r="W86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Forteo</t>
+          <t>Zepatier</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -23804,12 +23804,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Osteoporosis</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -23824,52 +23824,52 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2017Q4</t>
+          <t>2016Q1</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>2024Q3</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="I87" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1651.7</v>
+        <v>1659</v>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2017Q4-2018Q3</t>
+          <t>2017Q1-2017Q4</t>
         </is>
       </c>
       <c r="M87" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>365.7</v>
+        <v>167</v>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>2023Q4-2024Q3</t>
+          <t>2020Q1-2020Q4</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>0.221</v>
+        <v>0.101</v>
       </c>
       <c r="Q87" s="4" t="n"/>
       <c r="R87" s="3" t="n"/>
       <c r="S87" s="3" t="n"/>
       <c r="T87" s="3" t="n"/>
       <c r="U87" s="3" t="n">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="V87" s="3" t="inlineStr">
         <is>
-          <t>bone_anabolic</t>
+          <t>hcv_ns5a_protease_combination</t>
         </is>
       </c>
       <c r="W87" s="3" t="inlineStr">
@@ -23881,7 +23881,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Breyanzi</t>
+          <t>Forteo</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -23891,12 +23891,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Osteoporosis</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -23911,60 +23911,64 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021Q2</t>
+          <t>2017Q4</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2024Q3</t>
         </is>
       </c>
       <c r="I88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1646</v>
+        <v>1651.7</v>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2017Q4-2018Q3</t>
         </is>
       </c>
       <c r="M88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>1646</v>
+        <v>365.7</v>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q4-2024Q3</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>1</v>
+        <v>0.221</v>
       </c>
       <c r="Q88" s="4" t="n"/>
       <c r="R88" s="3" t="n"/>
       <c r="S88" s="3" t="n"/>
       <c r="T88" s="3" t="n"/>
       <c r="U88" s="3" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="V88" s="3" t="inlineStr">
         <is>
-          <t>cd19_car_t</t>
-        </is>
-      </c>
-      <c r="W88" s="3" t="n"/>
+          <t>bone_anabolic</t>
+        </is>
+      </c>
+      <c r="W88" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Nurtec ODT</t>
+          <t>Breyanzi</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -23974,12 +23978,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -23994,7 +23998,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2021Q2</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -24006,10 +24010,10 @@
         <v>1</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1591</v>
+        <v>1646</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
@@ -24020,7 +24024,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>1591</v>
+        <v>1646</v>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
@@ -24035,11 +24039,11 @@
       <c r="S89" s="3" t="n"/>
       <c r="T89" s="3" t="n"/>
       <c r="U89" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="V89" s="3" t="inlineStr">
         <is>
-          <t>cgrp_receptor_antagonist</t>
+          <t>cd19_car_t</t>
         </is>
       </c>
       <c r="W89" s="3" t="n"/>
@@ -24047,7 +24051,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Reyataz</t>
+          <t>Nurtec ODT</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -24057,17 +24061,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Worldwide net sales of Reyataz alone (the row labelled "Reyataz"), excluding Evotaz</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -24077,64 +24081,60 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2003Q2</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>2014Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1571</v>
+        <v>1591</v>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2011Q3-2012Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>1362</v>
+        <v>1591</v>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>2014Q1-2014Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="4" t="n"/>
       <c r="R90" s="3" t="n"/>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="n"/>
       <c r="U90" s="3" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="V90" s="3" t="inlineStr">
         <is>
-          <t>hiv_protease_inhibitor</t>
-        </is>
-      </c>
-      <c r="W90" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>cgrp_receptor_antagonist</t>
+        </is>
+      </c>
+      <c r="W90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Myrbetriq</t>
+          <t>Reyataz</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -24144,17 +24144,17 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Astellas</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>GI / Liver / Women's Health / Urology</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide net sales of Reyataz alone (the row labelled "Reyataz"), excluding Evotaz</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -24164,60 +24164,64 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2017Q2</t>
+          <t>2003Q2</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2014Q4</t>
         </is>
       </c>
       <c r="I91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1569.113</v>
+        <v>1571</v>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>2020Q3-2021Q2</t>
+          <t>2011Q3-2012Q2</t>
         </is>
       </c>
       <c r="M91" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>1355.966</v>
+        <v>1362</v>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2014Q1-2014Q4</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0.864</v>
+        <v>0.867</v>
       </c>
       <c r="Q91" s="4" t="n"/>
       <c r="R91" s="3" t="n"/>
       <c r="S91" s="3" t="n"/>
       <c r="T91" s="3" t="n"/>
       <c r="U91" s="3" t="n">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="V91" s="3" t="inlineStr">
         <is>
-          <t>beta3_adrenergic_receptor_agonist</t>
-        </is>
-      </c>
-      <c r="W91" s="3" t="n"/>
+          <t>hiv_protease_inhibitor</t>
+        </is>
+      </c>
+      <c r="W91" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Baraclude</t>
+          <t>Myrbetriq</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -24227,12 +24231,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Astellas</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>GI / Liver / Women's Health / Urology</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -24247,64 +24251,60 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2005Q2</t>
+          <t>2016Q2</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>2021Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I92" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1567</v>
+        <v>1569.113</v>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2013Q2-2014Q1</t>
+          <t>2020Q3-2021Q2</t>
         </is>
       </c>
       <c r="M92" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>431</v>
+        <v>1355.966</v>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>2020Q4-2021Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.275</v>
+        <v>0.864</v>
       </c>
       <c r="Q92" s="4" t="n"/>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3" t="n"/>
       <c r="T92" s="3" t="n"/>
       <c r="U92" s="3" t="n">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="V92" s="3" t="inlineStr">
         <is>
-          <t>hbv_nucleoside_analogue</t>
-        </is>
-      </c>
-      <c r="W92" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>beta3_adrenergic_receptor_agonist</t>
+        </is>
+      </c>
+      <c r="W92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Pulmicort Flexhaler</t>
+          <t>Baraclude</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -24314,17 +24314,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Worldwide Pulmicort brand total (all formulations: Turbuhaler, Respules, Flexhaler); Flexhaler is not printed separately</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -24334,60 +24334,64 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2001Q3</t>
+          <t>2005Q2</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2021Q3</t>
         </is>
       </c>
       <c r="I93" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1545</v>
+        <v>1567</v>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>2007Q4-2008Q3</t>
+          <t>2013Q2-2014Q1</t>
         </is>
       </c>
       <c r="M93" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>523</v>
+        <v>431</v>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2020Q4-2021Q3</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>0.339</v>
+        <v>0.275</v>
       </c>
       <c r="Q93" s="4" t="n"/>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3" t="n"/>
       <c r="T93" s="3" t="n"/>
       <c r="U93" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="V93" s="3" t="inlineStr">
         <is>
-          <t>inhaled_corticosteroid</t>
-        </is>
-      </c>
-      <c r="W93" s="3" t="n"/>
+          <t>hbv_nucleoside_analogue</t>
+        </is>
+      </c>
+      <c r="W93" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Abilify Maintena</t>
+          <t>Pulmicort Flexhaler</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -24397,17 +24401,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Worldwide 1-month long-acting injection</t>
+          <t>Worldwide Pulmicort brand total (all formulations: Turbuhaler, Respules, Flexhaler); Flexhaler is not printed separately</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -24417,7 +24421,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2014Q1</t>
+          <t>2001Q3</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -24429,21 +24433,21 @@
         <v>1</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1542.055</v>
+        <v>1545</v>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2007Q4-2008Q3</t>
         </is>
       </c>
       <c r="M94" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>1542.055</v>
+        <v>523</v>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
@@ -24451,18 +24455,18 @@
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>1</v>
+        <v>0.339</v>
       </c>
       <c r="Q94" s="4" t="n"/>
       <c r="R94" s="3" t="n"/>
       <c r="S94" s="3" t="n"/>
       <c r="T94" s="3" t="n"/>
       <c r="U94" s="3" t="n">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="V94" s="3" t="inlineStr">
         <is>
-          <t>dopamine_serotonin_partial_agonist</t>
+          <t>inhaled_corticosteroid</t>
         </is>
       </c>
       <c r="W94" s="3" t="n"/>
@@ -24470,7 +24474,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Complera</t>
+          <t>Abilify Maintena</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -24480,17 +24484,17 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide 1-month long-acting injection</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -24500,64 +24504,60 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2011Q3</t>
+          <t>2014Q1</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I95" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="3" t="n">
         <v>50</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1540</v>
+        <v>1542.055</v>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>2015Q4-2016Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M95" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>129</v>
+        <v>1542.055</v>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>2023Q1-2023Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="4" t="n"/>
       <c r="R95" s="3" t="n"/>
       <c r="S95" s="3" t="n"/>
       <c r="T95" s="3" t="n"/>
       <c r="U95" s="3" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="V95" s="3" t="inlineStr">
         <is>
-          <t>hiv_antiretroviral</t>
-        </is>
-      </c>
-      <c r="W95" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>dopamine_serotonin_partial_agonist</t>
+        </is>
+      </c>
+      <c r="W95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Crysvita</t>
+          <t>Complera</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -24567,12 +24567,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -24587,60 +24587,64 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2020Q1</t>
+          <t>2011Q3</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="I96" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1520.311</v>
+        <v>1540</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2015Q4-2016Q3</t>
         </is>
       </c>
       <c r="M96" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>1520.311</v>
+        <v>129</v>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q1-2023Q4</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>1</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q96" s="4" t="n"/>
       <c r="R96" s="3" t="n"/>
       <c r="S96" s="3" t="n"/>
       <c r="T96" s="3" t="n"/>
       <c r="U96" s="3" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="V96" s="3" t="inlineStr">
         <is>
-          <t>fgf23_blocking_antibody</t>
-        </is>
-      </c>
-      <c r="W96" s="3" t="n"/>
+          <t>hiv_antiretroviral</t>
+        </is>
+      </c>
+      <c r="W96" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Takhzyro</t>
+          <t>Crysvita</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -24650,7 +24654,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Takeda</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -24670,7 +24674,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2019Q1</t>
+          <t>2020Q1</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -24682,21 +24686,21 @@
         <v>1</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1511.319</v>
+        <v>1520.311</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>2024Q4-2025Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M97" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>1482.742</v>
+        <v>1520.311</v>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
@@ -24704,7 +24708,7 @@
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="4" t="n"/>
       <c r="R97" s="3" t="n"/>
@@ -24715,7 +24719,7 @@
       </c>
       <c r="V97" s="3" t="inlineStr">
         <is>
-          <t>plasma_kallikrein_inhibitor</t>
+          <t>fgf23_blocking_antibody</t>
         </is>
       </c>
       <c r="W97" s="3" t="n"/>
@@ -24723,7 +24727,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Altuviiio</t>
+          <t>Takhzyro</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -24733,7 +24737,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Takeda</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -24753,7 +24757,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2023Q2</t>
+          <t>2019Q1</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -24765,21 +24769,21 @@
         <v>1</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1507.007</v>
+        <v>1511.319</v>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q4-2025Q3</t>
         </is>
       </c>
       <c r="M98" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>1507.007</v>
+        <v>1482.742</v>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
@@ -24787,18 +24791,18 @@
         </is>
       </c>
       <c r="P98" s="3" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="Q98" s="4" t="n"/>
       <c r="R98" s="3" t="n"/>
       <c r="S98" s="3" t="n"/>
       <c r="T98" s="3" t="n"/>
       <c r="U98" s="3" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="V98" s="3" t="inlineStr">
         <is>
-          <t>factor_viii_replacement</t>
+          <t>plasma_kallikrein_inhibitor</t>
         </is>
       </c>
       <c r="W98" s="3" t="n"/>
@@ -24806,7 +24810,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Betaseron</t>
+          <t>Altuviiio</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -24816,12 +24820,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -24836,59 +24840,55 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2012Q4</t>
+          <t>2023Q2</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I99" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1453.106</v>
+        <v>1507.007</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>2012Q4-2013Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M99" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>207.558</v>
+        <v>1507.007</v>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>2024Q1-2024Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="4" t="n"/>
       <c r="R99" s="3" t="n"/>
       <c r="S99" s="3" t="n"/>
       <c r="T99" s="3" t="n"/>
       <c r="U99" s="3" t="n">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="V99" s="3" t="inlineStr">
         <is>
-          <t>interferon_beta</t>
-        </is>
-      </c>
-      <c r="W99" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>factor_viii_replacement</t>
+        </is>
+      </c>
+      <c r="W99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -25569,7 +25569,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Lorbrena</t>
+          <t>Cerezyme</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -25579,12 +25579,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Genzyme</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2019Q3</t>
+          <t>1999Q1</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
@@ -25611,21 +25611,21 @@
         <v>1</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1209</v>
+        <v>1238.977</v>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2008Q1-2008Q4</t>
         </is>
       </c>
       <c r="M108" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>1209</v>
+        <v>797.9640000000001</v>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
@@ -25633,18 +25633,18 @@
         </is>
       </c>
       <c r="P108" s="3" t="n">
-        <v>1</v>
+        <v>0.644</v>
       </c>
       <c r="Q108" s="4" t="n"/>
       <c r="R108" s="3" t="n"/>
       <c r="S108" s="3" t="n"/>
       <c r="T108" s="3" t="n"/>
       <c r="U108" s="3" t="n">
-        <v>2018</v>
+        <v>1994</v>
       </c>
       <c r="V108" s="3" t="inlineStr">
         <is>
-          <t>alk_inhibitor</t>
+          <t>enzyme_replacement_therapy</t>
         </is>
       </c>
       <c r="W108" s="3" t="n"/>
@@ -25652,7 +25652,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Viread</t>
+          <t>Lorbrena</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -25662,12 +25662,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -25682,64 +25682,60 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2002Q1</t>
+          <t>2019Q3</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I109" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1187</v>
+        <v>1209</v>
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>2016Q3-2017Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M109" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" s="4" t="n">
-        <v>82</v>
+        <v>1209</v>
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>2023Q1-2023Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="4" t="n"/>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3" t="n"/>
       <c r="T109" s="3" t="n"/>
       <c r="U109" s="3" t="n">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="V109" s="3" t="inlineStr">
         <is>
-          <t>nucleotide_reverse_transcriptase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W109" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>alk_inhibitor</t>
+        </is>
+      </c>
+      <c r="W109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Fabrazyme</t>
+          <t>Viread</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -25749,12 +25745,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Genzyme</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -25769,60 +25765,64 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2002Q3</t>
+          <t>2002Q1</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="I110" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1186.37</v>
+        <v>1187</v>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2016Q3-2017Q2</t>
         </is>
       </c>
       <c r="M110" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>1186.37</v>
+        <v>82</v>
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q1-2023Q4</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
-        <v>1</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Q110" s="4" t="n"/>
       <c r="R110" s="3" t="n"/>
       <c r="S110" s="3" t="n"/>
       <c r="T110" s="3" t="n"/>
       <c r="U110" s="3" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="V110" s="3" t="inlineStr">
         <is>
-          <t>enzyme_replacement_therapy</t>
-        </is>
-      </c>
-      <c r="W110" s="3" t="n"/>
+          <t>nucleotide_reverse_transcriptase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W110" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Basaglar</t>
+          <t>Fabrazyme</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -25832,12 +25832,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Genzyme</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -25852,64 +25852,60 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2017Q4</t>
+          <t>2002Q3</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I111" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1164.8</v>
+        <v>1186.37</v>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>2019Q2-2020Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M111" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" s="4" t="n">
-        <v>676.9</v>
+        <v>1186.37</v>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>2024Q1-2024Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0.581</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="4" t="n"/>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3" t="n"/>
       <c r="T111" s="3" t="n"/>
       <c r="U111" s="3" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="V111" s="3" t="inlineStr">
         <is>
-          <t>insulin</t>
-        </is>
-      </c>
-      <c r="W111" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>enzyme_replacement_therapy</t>
+        </is>
+      </c>
+      <c r="W111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Nplate</t>
+          <t>Basaglar</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -25919,80 +25915,84 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Diabetes</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2017Q4</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="I112" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1156</v>
+        <v>1164.8</v>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2019Q2-2020Q1</t>
         </is>
       </c>
       <c r="M112" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1156</v>
+        <v>676.9</v>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q1-2024Q4</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
-        <v>1</v>
+        <v>0.581</v>
       </c>
       <c r="Q112" s="4" t="n"/>
       <c r="R112" s="3" t="n"/>
       <c r="S112" s="3" t="n"/>
       <c r="T112" s="3" t="n"/>
       <c r="U112" s="3" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="V112" s="3" t="inlineStr">
         <is>
-          <t>thrombopoietin_receptor_agonist</t>
-        </is>
-      </c>
-      <c r="W112" s="3" t="n"/>
+          <t>insulin</t>
+        </is>
+      </c>
+      <c r="W112" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Abrysvo</t>
+          <t>Nplate</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -26002,27 +26002,27 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2009Q1</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
@@ -26034,10 +26034,10 @@
         <v>1</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>1</v>
       </c>
       <c r="N113" s="4" t="n">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
@@ -26063,11 +26063,11 @@
       <c r="S113" s="3" t="n"/>
       <c r="T113" s="3" t="n"/>
       <c r="U113" s="3" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="V113" s="3" t="inlineStr">
         <is>
-          <t>recombinant_protein_vaccine</t>
+          <t>thrombopoietin_receptor_agonist</t>
         </is>
       </c>
       <c r="W113" s="3" t="n"/>
@@ -26075,7 +26075,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Caplyta</t>
+          <t>Abrysvo</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -26085,27 +26085,27 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Intra-Cellular Therapies</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>U.S. net product sales: Intra-Cellular Therapies' 'Product sales, net' (its only product line, CAPLYTA, sold in the U.S.) through 2024Q4, then Johnson &amp; Johnson's CAPLYTA US row (Intl row nil) from 2025Q2</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2020Q1</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
@@ -26117,10 +26117,10 @@
         <v>1</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>1</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
@@ -26146,11 +26146,11 @@
       <c r="S114" s="3" t="n"/>
       <c r="T114" s="3" t="n"/>
       <c r="U114" s="3" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="V114" s="3" t="inlineStr">
         <is>
-          <t>atypical_antipsychotic</t>
+          <t>recombinant_protein_vaccine</t>
         </is>
       </c>
       <c r="W114" s="3" t="n"/>
@@ -26158,7 +26158,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Linzess</t>
+          <t>Caplyta</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -26168,27 +26168,27 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Allergan plc</t>
+          <t>Intra-Cellular Therapies</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>GI / Liver / Women's Health / Urology</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>U.S. net product sales: Intra-Cellular Therapies' 'Product sales, net' (its only product line, CAPLYTA, sold in the U.S.) through 2024Q4, then Johnson &amp; Johnson's CAPLYTA US row (Intl row nil) from 2025Q2</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (U.S. Linzess plus Int'l., labelled Linzess/Constella)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2014Q3</t>
+          <t>2020Q1</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
@@ -26200,21 +26200,21 @@
         <v>1</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>2023Q2-2024Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M115" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N115" s="4" t="n">
-        <v>1079</v>
+        <v>1120</v>
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
@@ -26222,18 +26222,18 @@
         </is>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0.968</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="4" t="n"/>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3" t="n"/>
       <c r="T115" s="3" t="n"/>
       <c r="U115" s="3" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="V115" s="3" t="inlineStr">
         <is>
-          <t>guanylate_cyclase_c_agonist</t>
+          <t>atypical_antipsychotic</t>
         </is>
       </c>
       <c r="W115" s="3" t="n"/>
@@ -26241,7 +26241,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Vemlidy</t>
+          <t>Linzess</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -26251,12 +26251,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Allergan plc</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Infectious Disease / Vaccines</t>
+          <t>GI / Liver / Women's Health / Urology</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -26266,12 +26266,12 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (U.S. Linzess plus Int'l., labelled Linzess/Constella)</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2017Q1</t>
+          <t>2014Q3</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -26283,21 +26283,21 @@
         <v>1</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q2-2024Q1</t>
         </is>
       </c>
       <c r="M116" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
@@ -26305,18 +26305,18 @@
         </is>
       </c>
       <c r="P116" s="3" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
       <c r="Q116" s="4" t="n"/>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3" t="n"/>
       <c r="T116" s="3" t="n"/>
       <c r="U116" s="3" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="V116" s="3" t="inlineStr">
         <is>
-          <t>nucleotide_reverse_transcriptase_inhibitor</t>
+          <t>guanylate_cyclase_c_agonist</t>
         </is>
       </c>
       <c r="W116" s="3" t="n"/>
@@ -26324,7 +26324,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Cyramza</t>
+          <t>Vemlidy</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -26334,12 +26334,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Infectious Disease / Vaccines</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -26354,64 +26354,60 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2017Q4</t>
+          <t>2017Q1</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1046.8</v>
+        <v>1093</v>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>2020Q4-2021Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N117" s="4" t="n">
-        <v>973.4</v>
+        <v>1093</v>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>2024Q1-2024Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P117" s="3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="Q117" s="4" t="n"/>
       <c r="R117" s="3" t="n"/>
       <c r="S117" s="3" t="n"/>
       <c r="T117" s="3" t="n"/>
       <c r="U117" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="V117" s="3" t="inlineStr">
         <is>
-          <t>monoclonal_antibody</t>
-        </is>
-      </c>
-      <c r="W117" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>nucleotide_reverse_transcriptase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Opzelura</t>
+          <t>Cyramza</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -26421,12 +26417,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Immunology / Inflammation</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -26441,60 +26437,64 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021Q4</t>
+          <t>2017Q4</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="I118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>988.002</v>
+        <v>1046.8</v>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2020Q4-2021Q3</t>
         </is>
       </c>
       <c r="M118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>988.002</v>
+        <v>973.4</v>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q1-2024Q4</t>
         </is>
       </c>
       <c r="P118" s="3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="Q118" s="4" t="n"/>
       <c r="R118" s="3" t="n"/>
       <c r="S118" s="3" t="n"/>
       <c r="T118" s="3" t="n"/>
       <c r="U118" s="3" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="V118" s="3" t="inlineStr">
         <is>
-          <t>jak1_jak2_inhibitor</t>
-        </is>
-      </c>
-      <c r="W118" s="3" t="n"/>
+          <t>monoclonal_antibody</t>
+        </is>
+      </c>
+      <c r="W118" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Gattex</t>
+          <t>Opzelura</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -26504,12 +26504,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Takeda</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>GI / Liver / Women's Health / Urology</t>
+          <t>Immunology / Inflammation</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -26524,7 +26524,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2019Q1</t>
+          <t>2021Q4</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
@@ -26536,10 +26536,10 @@
         <v>1</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>985.398</v>
+        <v>988.002</v>
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>1</v>
       </c>
       <c r="N119" s="4" t="n">
-        <v>985.398</v>
+        <v>988.002</v>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
@@ -26565,11 +26565,11 @@
       <c r="S119" s="3" t="n"/>
       <c r="T119" s="3" t="n"/>
       <c r="U119" s="3" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="V119" s="3" t="inlineStr">
         <is>
-          <t>glp2_receptor_agonist</t>
+          <t>jak1_jak2_inhibitor</t>
         </is>
       </c>
       <c r="W119" s="3" t="n"/>
@@ -26577,7 +26577,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Uplizna</t>
+          <t>Gattex</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -26587,12 +26587,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Takeda</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>GI / Liver / Women's Health / Urology</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2019Q1</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
@@ -26619,10 +26619,10 @@
         <v>1</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>985</v>
+        <v>985.398</v>
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>1</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>985</v>
+        <v>985.398</v>
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
@@ -26648,11 +26648,11 @@
       <c r="S120" s="3" t="n"/>
       <c r="T120" s="3" t="n"/>
       <c r="U120" s="3" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="V120" s="3" t="inlineStr">
         <is>
-          <t>cd19_directed_antibody</t>
+          <t>glp2_receptor_agonist</t>
         </is>
       </c>
       <c r="W120" s="3" t="n"/>
@@ -26660,7 +26660,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Lovaza</t>
+          <t>Uplizna</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -26670,12 +26670,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Cardiometabolic / Renal</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -26690,64 +26690,60 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2008Q1</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>2016Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>972.978</v>
+        <v>985</v>
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>2011Q4-2012Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" s="4" t="n">
-        <v>58.632</v>
+        <v>985</v>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>2016Q1-2016Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="4" t="n"/>
       <c r="R121" s="3" t="n"/>
       <c r="S121" s="3" t="n"/>
       <c r="T121" s="3" t="n"/>
       <c r="U121" s="3" t="n">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="V121" s="3" t="inlineStr">
         <is>
-          <t>omega3_fatty_acid_triglyceride_lowering</t>
-        </is>
-      </c>
-      <c r="W121" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>cd19_directed_antibody</t>
+        </is>
+      </c>
+      <c r="W121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Nexviazyme</t>
+          <t>Lovaza</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -26757,12 +26753,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Cardiometabolic / Renal</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -26777,60 +26773,64 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2021Q4</t>
+          <t>2008Q1</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2016Q4</t>
         </is>
       </c>
       <c r="I122" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>967.013</v>
+        <v>972.978</v>
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2011Q4-2012Q3</t>
         </is>
       </c>
       <c r="M122" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>967.013</v>
+        <v>58.632</v>
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2016Q1-2016Q4</t>
         </is>
       </c>
       <c r="P122" s="3" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="Q122" s="4" t="n"/>
       <c r="R122" s="3" t="n"/>
       <c r="S122" s="3" t="n"/>
       <c r="T122" s="3" t="n"/>
       <c r="U122" s="3" t="n">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="V122" s="3" t="inlineStr">
         <is>
-          <t>enzyme_replacement_therapy</t>
-        </is>
-      </c>
-      <c r="W122" s="3" t="n"/>
+          <t>omega3_fatty_acid_triglyceride_lowering</t>
+        </is>
+      </c>
+      <c r="W122" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Rybrevant</t>
+          <t>Nexviazyme</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -26840,17 +26840,17 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Product family</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2021Q4</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -26872,10 +26872,10 @@
         <v>1</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>960</v>
+        <v>967.013</v>
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>1</v>
       </c>
       <c r="N123" s="4" t="n">
-        <v>960</v>
+        <v>967.013</v>
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
       </c>
       <c r="V123" s="3" t="inlineStr">
         <is>
-          <t>egfr_met_bispecific_antibody</t>
+          <t>enzyme_replacement_therapy</t>
         </is>
       </c>
       <c r="W123" s="3" t="n"/>
@@ -26913,7 +26913,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Cerezyme</t>
+          <t>Rybrevant</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -26923,17 +26923,17 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Product family</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -26943,7 +26943,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2011Q2</t>
+          <t>2024Q1</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
@@ -26955,21 +26955,21 @@
         <v>1</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>948.476</v>
+        <v>960</v>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>2013Q4-2014Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M124" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>797.9640000000001</v>
+        <v>960</v>
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
@@ -26977,18 +26977,18 @@
         </is>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0.841</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="4" t="n"/>
       <c r="R124" s="3" t="n"/>
       <c r="S124" s="3" t="n"/>
       <c r="T124" s="3" t="n"/>
       <c r="U124" s="3" t="n">
-        <v>1994</v>
+        <v>2021</v>
       </c>
       <c r="V124" s="3" t="inlineStr">
         <is>
-          <t>enzyme_replacement_therapy</t>
+          <t>egfr_met_bispecific_antibody</t>
         </is>
       </c>
       <c r="W124" s="3" t="n"/>
@@ -27419,7 +27419,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Tecvayli</t>
+          <t>Aricept</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -27429,80 +27429,84 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eisai</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Brand total</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (Eisai-recorded; Japan, China and Asia / Asia and Latin America itemised)</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2023Q1</t>
+          <t>2013Q2</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I130" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>815</v>
+        <v>827.381</v>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2013Q2-2014Q1</t>
         </is>
       </c>
       <c r="M130" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" s="4" t="n">
-        <v>815</v>
+        <v>170.813</v>
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2025Q2-2026Q1</t>
         </is>
       </c>
       <c r="P130" s="3" t="n">
-        <v>1</v>
+        <v>0.206</v>
       </c>
       <c r="Q130" s="4" t="n"/>
       <c r="R130" s="3" t="n"/>
       <c r="S130" s="3" t="n"/>
       <c r="T130" s="3" t="n"/>
       <c r="U130" s="3" t="n">
-        <v>2022</v>
+        <v>1996</v>
       </c>
       <c r="V130" s="3" t="inlineStr">
         <is>
-          <t>bcma_cd3_bispecific_antibody</t>
-        </is>
-      </c>
-      <c r="W130" s="3" t="n"/>
+          <t>acetylcholinesterase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W130" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Ryzodeg 70/30</t>
+          <t>Tecvayli</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -27512,12 +27516,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Cardiometabolic / Renal</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -27532,37 +27536,37 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2016Q1</t>
+          <t>2023Q1</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I131" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>813.2569999999999</v>
+        <v>815</v>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>2025Q1-2025Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M131" s="3" t="b">
         <v>1</v>
       </c>
       <c r="N131" s="4" t="n">
-        <v>813.2569999999999</v>
+        <v>815</v>
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>2025Q1-2025Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P131" s="3" t="n">
@@ -27573,23 +27577,19 @@
       <c r="S131" s="3" t="n"/>
       <c r="T131" s="3" t="n"/>
       <c r="U131" s="3" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="V131" s="3" t="inlineStr">
         <is>
-          <t>premix_insulin_analogue</t>
-        </is>
-      </c>
-      <c r="W131" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>bcma_cd3_bispecific_antibody</t>
+        </is>
+      </c>
+      <c r="W131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Bavencio</t>
+          <t>Ryzodeg 70/30</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -27599,12 +27599,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Merck KGaA</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Cardiometabolic / Renal</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -27619,60 +27619,64 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2018Q1</t>
+          <t>2016Q1</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="I132" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>800.453</v>
+        <v>813.2569999999999</v>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>2023Q3-2024Q2</t>
+          <t>2025Q1-2025Q4</t>
         </is>
       </c>
       <c r="M132" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" s="4" t="n">
-        <v>649.7430000000001</v>
+        <v>813.2569999999999</v>
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2025Q1-2025Q4</t>
         </is>
       </c>
       <c r="P132" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="4" t="n"/>
       <c r="R132" s="3" t="n"/>
       <c r="S132" s="3" t="n"/>
       <c r="T132" s="3" t="n"/>
       <c r="U132" s="3" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="V132" s="3" t="inlineStr">
         <is>
-          <t>pdl1_inhibitor</t>
-        </is>
-      </c>
-      <c r="W132" s="3" t="n"/>
+          <t>premix_insulin_analogue</t>
+        </is>
+      </c>
+      <c r="W132" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Namenda XR</t>
+          <t>Bavencio</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -27682,84 +27686,80 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Forest Laboratories</t>
+          <t>Merck KGaA</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Namenda XR net sales</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2013Q2</t>
+          <t>2018Q1</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>2018Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I133" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>781.8</v>
+        <v>800.453</v>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>2015Q2-2016Q1</t>
+          <t>2023Q3-2024Q2</t>
         </is>
       </c>
       <c r="M133" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N133" s="4" t="n">
-        <v>157.9</v>
+        <v>649.7430000000001</v>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>2017Q4-2018Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P133" s="3" t="n">
-        <v>0.202</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Q133" s="4" t="n"/>
       <c r="R133" s="3" t="n"/>
       <c r="S133" s="3" t="n"/>
       <c r="T133" s="3" t="n"/>
       <c r="U133" s="3" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="V133" s="3" t="inlineStr">
         <is>
-          <t>nmda_receptor_antagonist</t>
-        </is>
-      </c>
-      <c r="W133" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>pdl1_inhibitor</t>
+        </is>
+      </c>
+      <c r="W133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Ranexa</t>
+          <t>Namenda XR</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -27769,72 +27769,72 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Forest Laboratories</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Chronic angina</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
+          <t>Namenda XR net sales</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
           <t>U.S.</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2009Q2</t>
+          <t>2013Q2</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>2021Q4</t>
+          <t>2018Q3</t>
         </is>
       </c>
       <c r="I134" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>781</v>
+        <v>781.8</v>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
+          <t>2015Q2-2016Q1</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N134" s="4" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
           <t>2017Q4-2018Q3</t>
         </is>
       </c>
-      <c r="M134" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N134" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O134" s="3" t="inlineStr">
-        <is>
-          <t>2021Q1-2021Q4</t>
-        </is>
-      </c>
       <c r="P134" s="3" t="n">
-        <v>0.013</v>
+        <v>0.202</v>
       </c>
       <c r="Q134" s="4" t="n"/>
       <c r="R134" s="3" t="n"/>
       <c r="S134" s="3" t="n"/>
       <c r="T134" s="3" t="n"/>
       <c r="U134" s="3" t="n">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="V134" s="3" t="inlineStr">
         <is>
-          <t>antianginal</t>
+          <t>nmda_receptor_antagonist</t>
         </is>
       </c>
       <c r="W134" s="3" t="inlineStr">
@@ -27846,7 +27846,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Treanda</t>
+          <t>Ranexa</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -27856,72 +27856,72 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Cephalon</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Chronic angina</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Worldwide product net sales as reported by the owner</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2008Q2</t>
+          <t>2009Q2</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>2015Q4</t>
+          <t>2021Q4</t>
         </is>
       </c>
       <c r="I135" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>2014Q1-2014Q4</t>
+          <t>2017Q4-2018Q3</t>
         </is>
       </c>
       <c r="M135" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N135" s="4" t="n">
-        <v>741</v>
+        <v>10</v>
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>2015Q1-2015Q4</t>
+          <t>2021Q1-2021Q4</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
-        <v>0.955</v>
+        <v>0.013</v>
       </c>
       <c r="Q135" s="4" t="n"/>
       <c r="R135" s="3" t="n"/>
       <c r="S135" s="3" t="n"/>
       <c r="T135" s="3" t="n"/>
       <c r="U135" s="3" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="V135" s="3" t="inlineStr">
         <is>
-          <t>alkylating_agent_nitrogen_mustard</t>
+          <t>antianginal</t>
         </is>
       </c>
       <c r="W135" s="3" t="inlineStr">
@@ -27933,7 +27933,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Saphnelo</t>
+          <t>Treanda</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -27943,80 +27943,84 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Cephalon</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Immunology / Inflammation</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide product net sales as reported by the owner</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (World column; predominantly US, regional columns printed beside it)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2021Q3</t>
+          <t>2008Q2</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2015Q4</t>
         </is>
       </c>
       <c r="I136" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2014Q1-2014Q4</t>
         </is>
       </c>
       <c r="M136" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>763</v>
+        <v>741</v>
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2015Q1-2015Q4</t>
         </is>
       </c>
       <c r="P136" s="3" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="Q136" s="4" t="n"/>
       <c r="R136" s="3" t="n"/>
       <c r="S136" s="3" t="n"/>
       <c r="T136" s="3" t="n"/>
       <c r="U136" s="3" t="n">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="V136" s="3" t="inlineStr">
         <is>
-          <t>ifnar_antagonist_mab</t>
-        </is>
-      </c>
-      <c r="W136" s="3" t="n"/>
+          <t>alkylating_agent_nitrogen_mustard</t>
+        </is>
+      </c>
+      <c r="W136" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Trintellix</t>
+          <t>Saphnelo</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -28026,27 +28030,27 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Takeda</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Immunology / Inflammation</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide (World column; predominantly US, regional columns printed beside it)</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2015Q2</t>
+          <t>2021Q3</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
@@ -28058,10 +28062,10 @@
         <v>1</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>746.08</v>
+        <v>763</v>
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
@@ -28072,7 +28076,7 @@
         <v>1</v>
       </c>
       <c r="N137" s="4" t="n">
-        <v>746.08</v>
+        <v>763</v>
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
@@ -28087,11 +28091,11 @@
       <c r="S137" s="3" t="n"/>
       <c r="T137" s="3" t="n"/>
       <c r="U137" s="3" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="V137" s="3" t="inlineStr">
         <is>
-          <t>serotonin_modulator_and_stimulator</t>
+          <t>ifnar_antagonist_mab</t>
         </is>
       </c>
       <c r="W137" s="3" t="n"/>
@@ -28099,7 +28103,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Anoro Ellipta</t>
+          <t>Trintellix</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -28109,27 +28113,27 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Takeda</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2014Q2</t>
+          <t>2015Q2</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -28141,21 +28145,21 @@
         <v>1</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>740.279</v>
+        <v>746.08</v>
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>2024Q2-2025Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M138" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" s="4" t="n">
-        <v>719.497</v>
+        <v>746.08</v>
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
@@ -28163,7 +28167,7 @@
         </is>
       </c>
       <c r="P138" s="3" t="n">
-        <v>0.972</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="4" t="n"/>
       <c r="R138" s="3" t="n"/>
@@ -28174,7 +28178,7 @@
       </c>
       <c r="V138" s="3" t="inlineStr">
         <is>
-          <t>lama_laba_combination</t>
+          <t>serotonin_modulator_and_stimulator</t>
         </is>
       </c>
       <c r="W138" s="3" t="n"/>
@@ -28182,7 +28186,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Xultophy 100/3.6</t>
+          <t>Anoro Ellipta</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -28192,12 +28196,12 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Cardiometabolic / Renal</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -28212,64 +28216,60 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2017Q1</t>
+          <t>2014Q2</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I139" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>700.051</v>
+        <v>740.279</v>
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>2024Q4-2025Q3</t>
+          <t>2024Q2-2025Q1</t>
         </is>
       </c>
       <c r="M139" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N139" s="4" t="n">
-        <v>698.41</v>
+        <v>719.497</v>
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>2025Q1-2025Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
-        <v>0.998</v>
+        <v>0.972</v>
       </c>
       <c r="Q139" s="4" t="n"/>
       <c r="R139" s="3" t="n"/>
       <c r="S139" s="3" t="n"/>
       <c r="T139" s="3" t="n"/>
       <c r="U139" s="3" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="V139" s="3" t="inlineStr">
         <is>
-          <t>insulin_glp1_fixed_combination</t>
-        </is>
-      </c>
-      <c r="W139" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>lama_laba_combination</t>
+        </is>
+      </c>
+      <c r="W139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Radicava ORS</t>
+          <t>Xultophy 100/3.6</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -28279,72 +28279,72 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Mitsubishi Tanabe Pharma</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Cardiometabolic / Renal</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Product family</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (overseas ethical drugs line, predominantly U.S.)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2020Q2</t>
+          <t>2017Q1</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="I140" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>658.636</v>
+        <v>700.051</v>
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>2024Q2-2025Q1</t>
+          <t>2024Q4-2025Q3</t>
         </is>
       </c>
       <c r="M140" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" s="4" t="n">
-        <v>658.636</v>
+        <v>698.41</v>
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>2024Q2-2025Q1</t>
+          <t>2025Q1-2025Q4</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="Q140" s="4" t="n"/>
       <c r="R140" s="3" t="n"/>
       <c r="S140" s="3" t="n"/>
       <c r="T140" s="3" t="n"/>
       <c r="U140" s="3" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="V140" s="3" t="inlineStr">
         <is>
-          <t>free_radical_scavenger</t>
+          <t>insulin_glp1_fixed_combination</t>
         </is>
       </c>
       <c r="W140" s="3" t="inlineStr">
@@ -28356,7 +28356,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Bosulif</t>
+          <t>Radicava ORS</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -28366,80 +28366,84 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Mitsubishi Tanabe Pharma</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Product family</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (overseas ethical drugs line, predominantly U.S.)</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2016Q1</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="I141" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>655</v>
+        <v>658.636</v>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>2023Q4-2024Q3</t>
+          <t>2024Q2-2025Q1</t>
         </is>
       </c>
       <c r="M141" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N141" s="4" t="n">
-        <v>553</v>
+        <v>658.636</v>
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q2-2025Q1</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
-        <v>0.844</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="4" t="n"/>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3" t="n"/>
       <c r="T141" s="3" t="n"/>
       <c r="U141" s="3" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="V141" s="3" t="inlineStr">
         <is>
-          <t>tyrosine_kinase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W141" s="3" t="n"/>
+          <t>free_radical_scavenger</t>
+        </is>
+      </c>
+      <c r="W141" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Iressa</t>
+          <t>Bosulif</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -28449,7 +28453,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -28464,69 +28468,65 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (World column of AstraZeneca's quarterly Product Sales table; the regional columns beside it show emerging markets, US, Europe and established rest of world)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2002Q3</t>
+          <t>2016Q1</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I142" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" s="3" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>2012Q4-2013Q3</t>
+          <t>2023Q4-2024Q3</t>
         </is>
       </c>
       <c r="M142" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N142" s="4" t="n">
-        <v>115</v>
+        <v>553</v>
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>2022Q1-2022Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
-        <v>0.177</v>
+        <v>0.844</v>
       </c>
       <c r="Q142" s="4" t="n"/>
       <c r="R142" s="3" t="n"/>
       <c r="S142" s="3" t="n"/>
       <c r="T142" s="3" t="n"/>
       <c r="U142" s="3" t="n">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="V142" s="3" t="inlineStr">
         <is>
-          <t>egfr_tyrosine_kinase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W142" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>tyrosine_kinase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Stivarga</t>
+          <t>Iressa</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -28536,7 +28536,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -28551,65 +28551,69 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (World column of AstraZeneca's quarterly Product Sales table; the regional columns beside it show emerging markets, US, Europe and established rest of world)</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2012Q4</t>
+          <t>2002Q3</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="I143" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>645.016</v>
+        <v>649</v>
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
+          <t>2012Q4-2013Q3</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N143" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
           <t>2022Q1-2022Q4</t>
         </is>
       </c>
-      <c r="M143" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N143" s="4" t="n">
-        <v>355.809</v>
-      </c>
-      <c r="O143" s="3" t="inlineStr">
-        <is>
-          <t>2025Q3-2026Q2</t>
-        </is>
-      </c>
       <c r="P143" s="3" t="n">
-        <v>0.552</v>
+        <v>0.177</v>
       </c>
       <c r="Q143" s="4" t="n"/>
       <c r="R143" s="3" t="n"/>
       <c r="S143" s="3" t="n"/>
       <c r="T143" s="3" t="n"/>
       <c r="U143" s="3" t="n">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="V143" s="3" t="inlineStr">
         <is>
-          <t>multikinase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W143" s="3" t="n"/>
+          <t>egfr_tyrosine_kinase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W143" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>Doptelet</t>
+          <t>Stivarga</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -28619,27 +28623,27 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Sobi</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Doptelet product revenue as recorded by Sobi (its 'Doptelet' line, U.S. and Sobi's other markets), SEK; the line is the total Doptelet revenue Sobi recorded and also contains sales of Doptelet to Sobi's partner in China (volatile, low-margin, none in some quarters) and, in 2020Q2, a SEK 87 M milestone</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (Sobi-recorded)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2019Q4</t>
+          <t>2012Q4</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -28651,21 +28655,21 @@
         <v>1</v>
       </c>
       <c r="J144" s="3" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>639.059</v>
+        <v>645.016</v>
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2022Q1-2022Q4</t>
         </is>
       </c>
       <c r="M144" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" s="4" t="n">
-        <v>639.059</v>
+        <v>355.809</v>
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
@@ -28673,18 +28677,18 @@
         </is>
       </c>
       <c r="P144" s="3" t="n">
-        <v>1</v>
+        <v>0.552</v>
       </c>
       <c r="Q144" s="4" t="n"/>
       <c r="R144" s="3" t="n"/>
       <c r="S144" s="3" t="n"/>
       <c r="T144" s="3" t="n"/>
       <c r="U144" s="3" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="V144" s="3" t="inlineStr">
         <is>
-          <t>thrombopoietin_receptor_agonist</t>
+          <t>multikinase_inhibitor</t>
         </is>
       </c>
       <c r="W144" s="3" t="n"/>
@@ -28692,7 +28696,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Vectibix</t>
+          <t>Doptelet</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -28702,27 +28706,27 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Sobi</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Doptelet product revenue as recorded by Sobi (its 'Doptelet' line, U.S. and Sobi's other markets), SEK; the line is the total Doptelet revenue Sobi recorded and also contains sales of Doptelet to Sobi's partner in China (volatile, low-margin, none in some quarters) and, in 2020Q2, a SEK 87 M milestone</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide (Sobi-recorded)</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2009Q3</t>
+          <t>2019Q4</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -28734,10 +28738,10 @@
         <v>1</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>628</v>
+        <v>639.059</v>
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
@@ -28748,7 +28752,7 @@
         <v>1</v>
       </c>
       <c r="N145" s="4" t="n">
-        <v>628</v>
+        <v>639.059</v>
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
@@ -28763,11 +28767,11 @@
       <c r="S145" s="3" t="n"/>
       <c r="T145" s="3" t="n"/>
       <c r="U145" s="3" t="n">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="V145" s="3" t="inlineStr">
         <is>
-          <t>egfr_antibody</t>
+          <t>thrombopoietin_receptor_agonist</t>
         </is>
       </c>
       <c r="W145" s="3" t="n"/>
@@ -28775,7 +28779,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>Vascepa</t>
+          <t>Vectibix</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -28785,27 +28789,27 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Amarin</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Cardiometabolic / Renal</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Worldwide: Amarin company-total net product revenue</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (substantially all U.S. through 2019; ex-U.S. sales enter from 2018 and Europe from 2021, see notes)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2013Q1</t>
+          <t>2006Q4</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -28817,21 +28821,21 @@
         <v>1</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>616.253</v>
+        <v>628</v>
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>2020Q3-2021Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M146" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N146" s="4" t="n">
-        <v>177.504</v>
+        <v>628</v>
       </c>
       <c r="O146" s="3" t="inlineStr">
         <is>
@@ -28839,18 +28843,18 @@
         </is>
       </c>
       <c r="P146" s="3" t="n">
-        <v>0.288</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="4" t="n"/>
       <c r="R146" s="3" t="n"/>
       <c r="S146" s="3" t="n"/>
       <c r="T146" s="3" t="n"/>
       <c r="U146" s="3" t="n">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="V146" s="3" t="inlineStr">
         <is>
-          <t>omega3_epa_ethyl_ester</t>
+          <t>egfr_antibody</t>
         </is>
       </c>
       <c r="W146" s="3" t="n"/>
@@ -28858,7 +28862,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Bydureon BCise</t>
+          <t>Vascepa</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -28868,7 +28872,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Amarin</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -28878,74 +28882,70 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Worldwide product sales of the Bydureon franchise</t>
+          <t>Worldwide: Amarin company-total net product revenue</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (substantially all U.S. through 2019; ex-U.S. sales enter from 2018 and Europe from 2021, see notes)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2014Q2</t>
+          <t>2013Q1</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I147" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>608</v>
+        <v>616.253</v>
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>2015Q3-2016Q2</t>
+          <t>2020Q3-2021Q2</t>
         </is>
       </c>
       <c r="M147" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N147" s="4" t="n">
-        <v>162</v>
+        <v>177.504</v>
       </c>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>2023Q1-2023Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P147" s="3" t="n">
-        <v>0.266</v>
+        <v>0.288</v>
       </c>
       <c r="Q147" s="4" t="n"/>
       <c r="R147" s="3" t="n"/>
       <c r="S147" s="3" t="n"/>
       <c r="T147" s="3" t="n"/>
       <c r="U147" s="3" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="V147" s="3" t="inlineStr">
         <is>
-          <t>glp1_receptor_agonist</t>
-        </is>
-      </c>
-      <c r="W147" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>omega3_epa_ethyl_ester</t>
+        </is>
+      </c>
+      <c r="W147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Zeposia</t>
+          <t>Bydureon BCise</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -28955,17 +28955,17 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Immunology / Inflammation</t>
+          <t>Cardiometabolic / Renal</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide product sales of the Bydureon franchise</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -28975,60 +28975,64 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2020Q2</t>
+          <t>2014Q2</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="I148" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="3" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K148" s="4" t="n">
         <v>608</v>
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2015Q3-2016Q2</t>
         </is>
       </c>
       <c r="M148" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148" s="4" t="n">
-        <v>608</v>
+        <v>162</v>
       </c>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q1-2023Q4</t>
         </is>
       </c>
       <c r="P148" s="3" t="n">
-        <v>1</v>
+        <v>0.266</v>
       </c>
       <c r="Q148" s="4" t="n"/>
       <c r="R148" s="3" t="n"/>
       <c r="S148" s="3" t="n"/>
       <c r="T148" s="3" t="n"/>
       <c r="U148" s="3" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="V148" s="3" t="inlineStr">
         <is>
-          <t>s1p_receptor_modulator</t>
-        </is>
-      </c>
-      <c r="W148" s="3" t="n"/>
+          <t>glp1_receptor_agonist</t>
+        </is>
+      </c>
+      <c r="W148" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Leqembi</t>
+          <t>Zeposia</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -29038,12 +29042,12 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Eisai</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Immunology / Inflammation</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -29058,7 +29062,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -29070,10 +29074,10 @@
         <v>1</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>607.273</v>
+        <v>608</v>
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
@@ -29084,7 +29088,7 @@
         <v>1</v>
       </c>
       <c r="N149" s="4" t="n">
-        <v>607.273</v>
+        <v>608</v>
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
@@ -29099,11 +29103,11 @@
       <c r="S149" s="3" t="n"/>
       <c r="T149" s="3" t="n"/>
       <c r="U149" s="3" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="V149" s="3" t="inlineStr">
         <is>
-          <t>anti_amyloid_beta_antibody</t>
+          <t>s1p_receptor_modulator</t>
         </is>
       </c>
       <c r="W149" s="3" t="n"/>
@@ -29111,7 +29115,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Ebglyss</t>
+          <t>Leqembi</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -29121,12 +29125,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Eisai</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Immunology / Inflammation</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -29141,7 +29145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2024Q1</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
@@ -29153,10 +29157,10 @@
         <v>1</v>
       </c>
       <c r="J150" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>607</v>
+        <v>607.273</v>
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
@@ -29167,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="N150" s="4" t="n">
-        <v>607</v>
+        <v>607.273</v>
       </c>
       <c r="O150" s="3" t="inlineStr">
         <is>
@@ -29182,11 +29186,11 @@
       <c r="S150" s="3" t="n"/>
       <c r="T150" s="3" t="n"/>
       <c r="U150" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="V150" s="3" t="inlineStr">
         <is>
-          <t>il13_antagonist</t>
+          <t>anti_amyloid_beta_antibody</t>
         </is>
       </c>
       <c r="W150" s="3" t="n"/>
@@ -29194,7 +29198,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Xalkori</t>
+          <t>Ebglyss</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -29204,12 +29208,12 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Immunology / Inflammation</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -29224,64 +29228,60 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2012Q1</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I151" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>2017Q2-2018Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M151" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N151" s="4" t="n">
-        <v>374</v>
+        <v>607</v>
       </c>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>2023Q1-2023Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P151" s="3" t="n">
-        <v>0.617</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="4" t="n"/>
       <c r="R151" s="3" t="n"/>
       <c r="S151" s="3" t="n"/>
       <c r="T151" s="3" t="n"/>
       <c r="U151" s="3" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="V151" s="3" t="inlineStr">
         <is>
-          <t>tyrosine_kinase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W151" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>il13_antagonist</t>
+        </is>
+      </c>
+      <c r="W151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>Tradjenta</t>
+          <t>Xalkori</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -29291,17 +29291,17 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Cardiometabolic / Renal</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Collaboration revenue</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -29311,41 +29311,41 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2014Q1</t>
+          <t>2012Q1</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="I152" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>597.5</v>
+        <v>606</v>
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>2018Q4-2019Q3</t>
+          <t>2017Q2-2018Q1</t>
         </is>
       </c>
       <c r="M152" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N152" s="4" t="n">
-        <v>299.3</v>
+        <v>374</v>
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2023Q1-2023Q4</t>
         </is>
       </c>
       <c r="P152" s="3" t="n">
-        <v>0.501</v>
+        <v>0.617</v>
       </c>
       <c r="Q152" s="4" t="n"/>
       <c r="R152" s="3" t="n"/>
@@ -29356,15 +29356,19 @@
       </c>
       <c r="V152" s="3" t="inlineStr">
         <is>
-          <t>dpp4_inhibitor</t>
-        </is>
-      </c>
-      <c r="W152" s="3" t="n"/>
+          <t>tyrosine_kinase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W152" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Talvey</t>
+          <t>Tradjenta</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -29374,17 +29378,17 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Cardiometabolic / Renal</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Collaboration revenue</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -29394,7 +29398,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2014Q1</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
@@ -29406,21 +29410,21 @@
         <v>1</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>597</v>
+        <v>597.5</v>
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2018Q4-2019Q3</t>
         </is>
       </c>
       <c r="M153" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" s="4" t="n">
-        <v>597</v>
+        <v>299.3</v>
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
@@ -29428,18 +29432,18 @@
         </is>
       </c>
       <c r="P153" s="3" t="n">
-        <v>1</v>
+        <v>0.501</v>
       </c>
       <c r="Q153" s="4" t="n"/>
       <c r="R153" s="3" t="n"/>
       <c r="S153" s="3" t="n"/>
       <c r="T153" s="3" t="n"/>
       <c r="U153" s="3" t="n">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="V153" s="3" t="inlineStr">
         <is>
-          <t>gprc5d_cd3_bispecific_antibody</t>
+          <t>dpp4_inhibitor</t>
         </is>
       </c>
       <c r="W153" s="3" t="n"/>
@@ -29447,7 +29451,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Ayvakit</t>
+          <t>Talvey</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -29457,7 +29461,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Blueprint Medicines</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -29477,7 +29481,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2020Q1</t>
+          <t>2024Q1</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
@@ -29489,25 +29493,25 @@
         <v>1</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>596.722</v>
+        <v>597</v>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>2024Q3-2025Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M154" s="3" t="b">
         <v>1</v>
       </c>
       <c r="N154" s="4" t="n">
-        <v>596.722</v>
+        <v>597</v>
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>2024Q3-2025Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P154" s="3" t="n">
@@ -29518,11 +29522,11 @@
       <c r="S154" s="3" t="n"/>
       <c r="T154" s="3" t="n"/>
       <c r="U154" s="3" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="V154" s="3" t="inlineStr">
         <is>
-          <t>kit_pdgfra_kinase_inhibitor</t>
+          <t>gprc5d_cd3_bispecific_antibody</t>
         </is>
       </c>
       <c r="W154" s="3" t="n"/>
@@ -29530,7 +29534,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Kymriah</t>
+          <t>Ayvakit</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -29540,7 +29544,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Blueprint Medicines</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -29560,7 +29564,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2018Q1</t>
+          <t>2020Q1</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
@@ -29572,40 +29576,40 @@
         <v>1</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>587</v>
+        <v>596.722</v>
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>2021Q1-2021Q4</t>
+          <t>2024Q3-2025Q2</t>
         </is>
       </c>
       <c r="M155" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N155" s="4" t="n">
-        <v>351</v>
+        <v>596.722</v>
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2024Q3-2025Q2</t>
         </is>
       </c>
       <c r="P155" s="3" t="n">
-        <v>0.598</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="4" t="n"/>
       <c r="R155" s="3" t="n"/>
       <c r="S155" s="3" t="n"/>
       <c r="T155" s="3" t="n"/>
       <c r="U155" s="3" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="V155" s="3" t="inlineStr">
         <is>
-          <t>car_t_cell_therapy</t>
+          <t>kit_pdgfra_kinase_inhibitor</t>
         </is>
       </c>
       <c r="W155" s="3" t="n"/>
@@ -29613,7 +29617,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Skyclarys</t>
+          <t>Kymriah</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -29623,12 +29627,12 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -29638,12 +29642,12 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (U.S. only in 2023Q4; U.S. plus Rest of World from 2024Q1)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2018Q1</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
@@ -29655,21 +29659,21 @@
         <v>1</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>584.9</v>
+        <v>587</v>
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2021Q1-2021Q4</t>
         </is>
       </c>
       <c r="M156" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" s="4" t="n">
-        <v>584.9</v>
+        <v>351</v>
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
@@ -29677,18 +29681,18 @@
         </is>
       </c>
       <c r="P156" s="3" t="n">
-        <v>1</v>
+        <v>0.598</v>
       </c>
       <c r="Q156" s="4" t="n"/>
       <c r="R156" s="3" t="n"/>
       <c r="S156" s="3" t="n"/>
       <c r="T156" s="3" t="n"/>
       <c r="U156" s="3" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="V156" s="3" t="inlineStr">
         <is>
-          <t>nrf2_pathway_activator</t>
+          <t>car_t_cell_therapy</t>
         </is>
       </c>
       <c r="W156" s="3" t="n"/>
@@ -29696,7 +29700,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>AmBisome</t>
+          <t>Skyclarys</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -29706,12 +29710,12 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Gilead</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Invasive fungal infection</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -29721,12 +29725,12 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide (U.S. only in 2023Q4; U.S. plus Rest of World from 2024Q1)</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2005Q3</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
@@ -29738,21 +29742,21 @@
         <v>1</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>563</v>
+        <v>584.9</v>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>2021Q2-2022Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M157" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" s="4" t="n">
-        <v>489</v>
+        <v>584.9</v>
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
@@ -29760,18 +29764,18 @@
         </is>
       </c>
       <c r="P157" s="3" t="n">
-        <v>0.869</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="4" t="n"/>
       <c r="R157" s="3" t="n"/>
       <c r="S157" s="3" t="n"/>
       <c r="T157" s="3" t="n"/>
       <c r="U157" s="3" t="n">
-        <v>1997</v>
+        <v>2023</v>
       </c>
       <c r="V157" s="3" t="inlineStr">
         <is>
-          <t>antifungal</t>
+          <t>nrf2_pathway_activator</t>
         </is>
       </c>
       <c r="W157" s="3" t="n"/>
@@ -29779,7 +29783,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Zelnorm</t>
+          <t>AmBisome</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -29789,12 +29793,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Gilead</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>GI / Liver / Women's Health / Urology</t>
+          <t>Invasive fungal infection</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -29809,64 +29813,60 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2003Q1</t>
+          <t>2005Q3</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>2008Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I158" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>2006Q1-2006Q4</t>
+          <t>2021Q2-2022Q1</t>
         </is>
       </c>
       <c r="M158" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N158" s="4" t="n">
-        <v>10</v>
+        <v>489</v>
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>2008Q1-2008Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P158" s="3" t="n">
-        <v>0.018</v>
+        <v>0.869</v>
       </c>
       <c r="Q158" s="4" t="n"/>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3" t="n"/>
       <c r="T158" s="3" t="n"/>
       <c r="U158" s="3" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="V158" s="3" t="inlineStr">
         <is>
-          <t>serotonin_5ht4_receptor_agonist</t>
-        </is>
-      </c>
-      <c r="W158" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>antifungal</t>
+        </is>
+      </c>
+      <c r="W158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Ampyra</t>
+          <t>Zelnorm</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -29876,72 +29876,72 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Acorda Therapeutics</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>GI / Liver / Women's Health / Urology</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2010Q1</t>
+          <t>2003Q1</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2008Q4</t>
         </is>
       </c>
       <c r="I159" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>558.099</v>
+        <v>561</v>
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>2017Q4-2018Q3</t>
+          <t>2006Q1-2006Q4</t>
         </is>
       </c>
       <c r="M159" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N159" s="4" t="n">
-        <v>62.831</v>
+        <v>10</v>
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>2023Q2-2024Q1</t>
+          <t>2008Q1-2008Q4</t>
         </is>
       </c>
       <c r="P159" s="3" t="n">
-        <v>0.113</v>
+        <v>0.018</v>
       </c>
       <c r="Q159" s="4" t="n"/>
       <c r="R159" s="3" t="n"/>
       <c r="S159" s="3" t="n"/>
       <c r="T159" s="3" t="n"/>
       <c r="U159" s="3" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="V159" s="3" t="inlineStr">
         <is>
-          <t>potassium_channel_blocker</t>
+          <t>serotonin_5ht4_receptor_agonist</t>
         </is>
       </c>
       <c r="W159" s="3" t="inlineStr">
@@ -29953,7 +29953,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Orladeyo</t>
+          <t>Ampyra</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -29963,12 +29963,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>BioCryst Pharmaceuticals</t>
+          <t>Acorda Therapeutics</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Neurology / Psychiatry</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -29983,52 +29983,52 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2022Q1</t>
+          <t>2010Q1</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2024Q1</t>
         </is>
       </c>
       <c r="I160" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J160" s="3" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>548.779</v>
+        <v>558.099</v>
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>2025Q1-2025Q4</t>
+          <t>2017Q4-2018Q3</t>
         </is>
       </c>
       <c r="M160" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N160" s="4" t="n">
-        <v>548.779</v>
+        <v>62.831</v>
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>2025Q1-2025Q4</t>
+          <t>2023Q2-2024Q1</t>
         </is>
       </c>
       <c r="P160" s="3" t="n">
-        <v>1</v>
+        <v>0.113</v>
       </c>
       <c r="Q160" s="4" t="n"/>
       <c r="R160" s="3" t="n"/>
       <c r="S160" s="3" t="n"/>
       <c r="T160" s="3" t="n"/>
       <c r="U160" s="3" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="V160" s="3" t="inlineStr">
         <is>
-          <t>plasma_kallikrein_inhibitor</t>
+          <t>potassium_channel_blocker</t>
         </is>
       </c>
       <c r="W160" s="3" t="inlineStr">
@@ -30040,7 +30040,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Adynovate</t>
+          <t>Orladeyo</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -30050,7 +30050,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Takeda</t>
+          <t>BioCryst Pharmaceuticals</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -30060,70 +30060,74 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2019Q1</t>
+          <t>2022Q1</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="I161" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>548.255</v>
+        <v>548.779</v>
       </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>2021Q1-2021Q4</t>
+          <t>2025Q1-2025Q4</t>
         </is>
       </c>
       <c r="M161" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N161" s="4" t="n">
-        <v>365.824</v>
+        <v>548.779</v>
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2025Q1-2025Q4</t>
         </is>
       </c>
       <c r="P161" s="3" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="4" t="n"/>
       <c r="R161" s="3" t="n"/>
       <c r="S161" s="3" t="n"/>
       <c r="T161" s="3" t="n"/>
       <c r="U161" s="3" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="V161" s="3" t="inlineStr">
         <is>
-          <t>pegylated_recombinant_factor_viii</t>
-        </is>
-      </c>
-      <c r="W161" s="3" t="n"/>
+          <t>plasma_kallikrein_inhibitor</t>
+        </is>
+      </c>
+      <c r="W161" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Dulera</t>
+          <t>Adynovate</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -30133,12 +30137,12 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Takeda</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -30153,7 +30157,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2010Q3</t>
+          <t>2019Q1</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -30165,21 +30169,21 @@
         <v>1</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>536</v>
+        <v>548.255</v>
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>2015Q1-2015Q4</t>
+          <t>2021Q1-2021Q4</t>
         </is>
       </c>
       <c r="M162" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N162" s="4" t="n">
-        <v>145</v>
+        <v>365.824</v>
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
@@ -30187,18 +30191,18 @@
         </is>
       </c>
       <c r="P162" s="3" t="n">
-        <v>0.271</v>
+        <v>0.667</v>
       </c>
       <c r="Q162" s="4" t="n"/>
       <c r="R162" s="3" t="n"/>
       <c r="S162" s="3" t="n"/>
       <c r="T162" s="3" t="n"/>
       <c r="U162" s="3" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="V162" s="3" t="inlineStr">
         <is>
-          <t>ics_laba_combination</t>
+          <t>pegylated_recombinant_factor_viii</t>
         </is>
       </c>
       <c r="W162" s="3" t="n"/>
@@ -30206,7 +30210,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Dexilant</t>
+          <t>Dulera</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -30216,27 +30220,27 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Takeda</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>GI / Liver / Women's Health / Urology</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2014Q4</t>
+          <t>2010Q3</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
@@ -30248,21 +30252,21 @@
         <v>1</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>533.341</v>
+        <v>536</v>
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>2015Q2-2016Q1</t>
+          <t>2015Q1-2015Q4</t>
         </is>
       </c>
       <c r="M163" s="3" t="b">
         <v>0</v>
       </c>
       <c r="N163" s="4" t="n">
-        <v>46.461</v>
+        <v>145</v>
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
@@ -30270,18 +30274,18 @@
         </is>
       </c>
       <c r="P163" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.271</v>
       </c>
       <c r="Q163" s="4" t="n"/>
       <c r="R163" s="3" t="n"/>
       <c r="S163" s="3" t="n"/>
       <c r="T163" s="3" t="n"/>
       <c r="U163" s="3" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="V163" s="3" t="inlineStr">
         <is>
-          <t>proton_pump_inhibitor</t>
+          <t>ics_laba_combination</t>
         </is>
       </c>
       <c r="W163" s="3" t="n"/>
@@ -30289,7 +30293,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Aricept</t>
+          <t>Dexilant</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -30299,42 +30303,42 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Eisai</t>
+          <t>Takeda</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Neurology / Psychiatry</t>
+          <t>GI / Liver / Women's Health / Urology</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Brand total</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (Eisai-recorded; Japan, China and Asia / Asia and Latin America itemised)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2015Q2</t>
+          <t>2014Q4</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I164" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>525.76</v>
+        <v>533.341</v>
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
@@ -30345,33 +30349,29 @@
         <v>0</v>
       </c>
       <c r="N164" s="4" t="n">
-        <v>170.813</v>
+        <v>46.461</v>
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2025Q2-2026Q1</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P164" s="3" t="n">
-        <v>0.325</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q164" s="4" t="n"/>
       <c r="R164" s="3" t="n"/>
       <c r="S164" s="3" t="n"/>
       <c r="T164" s="3" t="n"/>
       <c r="U164" s="3" t="n">
-        <v>1996</v>
+        <v>2009</v>
       </c>
       <c r="V164" s="3" t="inlineStr">
         <is>
-          <t>acetylcholinesterase_inhibitor</t>
-        </is>
-      </c>
-      <c r="W164" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>proton_pump_inhibitor</t>
+        </is>
+      </c>
+      <c r="W164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2011Q1</t>
+          <t>2009Q1</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -32794,7 +32794,7 @@
         <v>1</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K193" s="4" t="n">
         <v>336.843</v>
@@ -35470,7 +35470,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Meda AB</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2021Q1</t>
+          <t>2012Q3</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
@@ -35502,7 +35502,7 @@
         <v>1</v>
       </c>
       <c r="J225" s="3" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K225" s="4" t="n">
         <v>200</v>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Provention Bio</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -38147,7 +38147,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -38159,7 +38159,7 @@
         <v>1</v>
       </c>
       <c r="J256" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K256" s="4" t="n">
         <v>82.795</v>

--- a/exports/peak_candidates.xlsx
+++ b/exports/peak_candidates.xlsx
@@ -22380,12 +22380,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Worldwide. 2006Q3-2013Q1: global in-market net sales of TYSABRI (Biogen plus Elan end-user sales at 100%) as stated in Biogen's earnings releases; 2013Q2 onward: Biogen's TYSABRI product revenue, worldwide total, which is the same 100% quantity once Biogen booked all of it.</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2013Q2</t>
+          <t>2006Q3</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -22397,7 +22397,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>2080.5</v>
@@ -25765,7 +25765,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2002Q1</t>
+          <t>2001Q4</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -25777,7 +25777,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>1187</v>
@@ -37257,7 +37257,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Bausch Health</t>
+          <t>Progenics Pharmaceuticals</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -37272,12 +37272,12 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>United States (U.S. sales of Salix products; the Salix segment is defined as sales in the U.S. of GI products)</t>
+          <t>United States. 2008Q2-2016Q4 rows: U.S. net sales of Relistor reported by the licensee (Wyeth, Salix, Valeant) to licensor Progenics Pharmaceuticals and stated in Progenics' 10-Q and 10-K; 2017Q1-2021Q4 rows: U.S. sales of Salix products in Bausch Health's earnings presentations.</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2017Q1</t>
+          <t>2008Q2</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="3" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="K246" s="4" t="n">
         <v>129</v>
@@ -38453,7 +38453,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>Astepro</t>
+          <t>Iluvien</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -38463,84 +38463,80 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Meda AB</t>
+          <t>Alimera Sciences</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Astepro brand net sales as printed by Meda AB, in SEK. Meda's prose labels the figure 'US sales' from 2008Q4 to 2010Q4; from 2011Q1 the figure is the Astepro row of Meda's group 'Sales trends for major products' table, which carries no geography label, and it equals the earlier US prose figure wherever the two overlap.</t>
+          <t>Worldwide ILUVIEN product revenue, net (ILUVIEN is the only commercial product through Q1 2023; ANI Pharmaceuticals rows from 2025Q3 are quarters in which ANI states no YUTIQ was sold). Through 2021Q1 and from 2021Q3 the 'Net revenue' line equals product revenue; 2021Q2 uses the 'Product revenue, net' line and excludes 11,048 thousand of license revenue.</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Worldwide (U.S. plus international; the total line is the sum of the U.S. and International columns)</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2008Q4</t>
+          <t>2013Q2</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>2014Q2</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I260" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260" s="3" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="K260" s="4" t="n">
-        <v>71.407</v>
+        <v>74.416</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>2011Q3-2012Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M260" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N260" s="4" t="n">
-        <v>33.27</v>
+        <v>74.416</v>
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>2013Q3-2014Q2</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P260" s="3" t="n">
-        <v>0.466</v>
+        <v>1</v>
       </c>
       <c r="Q260" s="4" t="n"/>
       <c r="R260" s="3" t="n"/>
       <c r="S260" s="3" t="n"/>
       <c r="T260" s="3" t="n"/>
       <c r="U260" s="3" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="V260" s="3" t="inlineStr">
         <is>
-          <t>h1_antihistamine_nasal</t>
-        </is>
-      </c>
-      <c r="W260" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>corticosteroid_intravitreal_implant</t>
+        </is>
+      </c>
+      <c r="W260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>Zynteglo</t>
+          <t>Astepro</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -38550,17 +38546,17 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>bluebird bio</t>
+          <t>Meda AB</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Rare Disease / Hematology</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Astepro brand net sales as printed by Meda AB, in SEK. Meda's prose labels the figure 'US sales' from 2008Q4 to 2010Q4; from 2011Q1 the figure is the Astepro row of Meda's group 'Sales trends for major products' table, which carries no geography label, and it equals the earlier US prose figure wherever the two overlap.</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -38570,52 +38566,52 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2023Q2</t>
+          <t>2008Q4</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2014Q2</t>
         </is>
       </c>
       <c r="I261" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K261" s="4" t="n">
-        <v>70.01900000000001</v>
+        <v>71.407</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>2024Q2-2025Q1</t>
+          <t>2011Q3-2012Q2</t>
         </is>
       </c>
       <c r="M261" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N261" s="4" t="n">
-        <v>70.01900000000001</v>
+        <v>33.27</v>
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>2024Q2-2025Q1</t>
+          <t>2013Q3-2014Q2</t>
         </is>
       </c>
       <c r="P261" s="3" t="n">
-        <v>1</v>
+        <v>0.466</v>
       </c>
       <c r="Q261" s="4" t="n"/>
       <c r="R261" s="3" t="n"/>
       <c r="S261" s="3" t="n"/>
       <c r="T261" s="3" t="n"/>
       <c r="U261" s="3" t="n">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="V261" s="3" t="inlineStr">
         <is>
-          <t>lentiviral_gene_therapy</t>
+          <t>h1_antihistamine_nasal</t>
         </is>
       </c>
       <c r="W261" s="3" t="inlineStr">
@@ -38627,7 +38623,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>Zyflo CR</t>
+          <t>Zynteglo</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -38637,17 +38633,17 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Critical Therapeutics</t>
+          <t>bluebird bio</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Rare Disease / Hematology</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>U.S. net product sales of the ZYFLO product family</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -38657,37 +38653,37 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2005Q4</t>
+          <t>2023Q2</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>2013Q3</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="I262" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J262" s="3" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="K262" s="4" t="n">
-        <v>64.98099999999999</v>
+        <v>70.01900000000001</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>2012Q4-2013Q3</t>
+          <t>2024Q2-2025Q1</t>
         </is>
       </c>
       <c r="M262" s="3" t="b">
         <v>1</v>
       </c>
       <c r="N262" s="4" t="n">
-        <v>64.98099999999999</v>
+        <v>70.01900000000001</v>
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>2012Q4-2013Q3</t>
+          <t>2024Q2-2025Q1</t>
         </is>
       </c>
       <c r="P262" s="3" t="n">
@@ -38698,11 +38694,11 @@
       <c r="S262" s="3" t="n"/>
       <c r="T262" s="3" t="n"/>
       <c r="U262" s="3" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="V262" s="3" t="inlineStr">
         <is>
-          <t>5_lipoxygenase_inhibitor</t>
+          <t>lentiviral_gene_therapy</t>
         </is>
       </c>
       <c r="W262" s="3" t="inlineStr">
@@ -38714,7 +38710,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Cotellic</t>
+          <t>Zyflo CR</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -38724,80 +38720,84 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Critical Therapeutics</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>U.S. net product sales of the ZYFLO product family</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2015Q4</t>
+          <t>2005Q4</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2013Q3</t>
         </is>
       </c>
       <c r="I263" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" s="3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K263" s="4" t="n">
-        <v>64.89700000000001</v>
+        <v>64.98099999999999</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>2017Q3-2018Q2</t>
+          <t>2012Q4-2013Q3</t>
         </is>
       </c>
       <c r="M263" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N263" s="4" t="n">
-        <v>56.738</v>
+        <v>64.98099999999999</v>
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2012Q4-2013Q3</t>
         </is>
       </c>
       <c r="P263" s="3" t="n">
-        <v>0.874</v>
+        <v>1</v>
       </c>
       <c r="Q263" s="4" t="n"/>
       <c r="R263" s="3" t="n"/>
       <c r="S263" s="3" t="n"/>
       <c r="T263" s="3" t="n"/>
       <c r="U263" s="3" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="V263" s="3" t="inlineStr">
         <is>
-          <t>mek_inhibitor</t>
-        </is>
-      </c>
-      <c r="W263" s="3" t="n"/>
+          <t>5_lipoxygenase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W263" s="3" t="inlineStr">
+        <is>
+          <t>issuer_stopped_reporting</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Vanflyta</t>
+          <t>Cotellic</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -38807,7 +38807,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -38817,17 +38817,17 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Vanflyta revenue row in Daiichi Sankyo's table 'Revenue by Business Units and Products', Oncology Business Unit section</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>The table prints no geography for the row; the Japan Business Unit product list in the same table does not list Vanflyta. Daiichi Sankyo's pipeline pages give the brand as 'VANFLYTA (JP/US/EU/CN)'.</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2015Q4</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -38839,21 +38839,21 @@
         <v>1</v>
       </c>
       <c r="J264" s="3" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="K264" s="4" t="n">
-        <v>59.382</v>
+        <v>64.89700000000001</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>2025Q3-2026Q2</t>
+          <t>2017Q3-2018Q2</t>
         </is>
       </c>
       <c r="M264" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N264" s="4" t="n">
-        <v>59.382</v>
+        <v>56.738</v>
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
@@ -38861,18 +38861,18 @@
         </is>
       </c>
       <c r="P264" s="3" t="n">
-        <v>1</v>
+        <v>0.874</v>
       </c>
       <c r="Q264" s="4" t="n"/>
       <c r="R264" s="3" t="n"/>
       <c r="S264" s="3" t="n"/>
       <c r="T264" s="3" t="n"/>
       <c r="U264" s="3" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="V264" s="3" t="inlineStr">
         <is>
-          <t>flt3_kinase_inhibitor</t>
+          <t>mek_inhibitor</t>
         </is>
       </c>
       <c r="W264" s="3" t="n"/>
@@ -38880,7 +38880,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>Bevespi Aerosphere</t>
+          <t>Vanflyta</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -38890,84 +38890,80 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>Respiratory / Allergy</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>Worldwide product sales</t>
+          <t>Vanflyta revenue row in Daiichi Sankyo's table 'Revenue by Business Units and Products', Oncology Business Unit section</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>The table prints no geography for the row; the Japan Business Unit product list in the same table does not list Vanflyta. Daiichi Sankyo's pipeline pages give the brand as 'VANFLYTA (JP/US/EU/CN)'.</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2017Q1</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="I265" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265" s="3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K265" s="4" t="n">
-        <v>59</v>
+        <v>59.382</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>2021Q4-2022Q3</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="M265" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N265" s="4" t="n">
-        <v>58</v>
+        <v>59.382</v>
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>2023Q1-2023Q4</t>
+          <t>2025Q3-2026Q2</t>
         </is>
       </c>
       <c r="P265" s="3" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="Q265" s="4" t="n"/>
       <c r="R265" s="3" t="n"/>
       <c r="S265" s="3" t="n"/>
       <c r="T265" s="3" t="n"/>
       <c r="U265" s="3" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="V265" s="3" t="inlineStr">
         <is>
-          <t>lama_laba_combination</t>
-        </is>
-      </c>
-      <c r="W265" s="3" t="inlineStr">
-        <is>
-          <t>issuer_stopped_reporting</t>
-        </is>
-      </c>
+          <t>flt3_kinase_inhibitor</t>
+        </is>
+      </c>
+      <c r="W265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>Iluvien</t>
+          <t>Bevespi Aerosphere</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -38977,77 +38973,77 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Alimera Sciences</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Respiratory / Allergy</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Worldwide ILUVIEN product revenue, net (ILUVIEN is the only commercial product through Q1 2023). Through 2021Q1 and from 2021Q3 the 'Net revenue' line equals product revenue; 2021Q2 uses the 'Product revenue, net' line and excludes 11,048 thousand of license revenue.</t>
+          <t>Worldwide product sales</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Worldwide (U.S. plus international; the total line is the sum of the U.S. and International columns)</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2013Q2</t>
+          <t>2017Q1</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>2023Q1</t>
+          <t>2023Q4</t>
         </is>
       </c>
       <c r="I266" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J266" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K266" s="4" t="n">
-        <v>55.777</v>
+        <v>59</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>2022Q2-2023Q1</t>
+          <t>2021Q4-2022Q3</t>
         </is>
       </c>
       <c r="M266" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N266" s="4" t="n">
-        <v>55.777</v>
+        <v>58</v>
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>2022Q2-2023Q1</t>
+          <t>2023Q1-2023Q4</t>
         </is>
       </c>
       <c r="P266" s="3" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="Q266" s="4" t="n"/>
       <c r="R266" s="3" t="n"/>
       <c r="S266" s="3" t="n"/>
       <c r="T266" s="3" t="n"/>
       <c r="U266" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="V266" s="3" t="inlineStr">
         <is>
-          <t>corticosteroid_intravitreal_implant</t>
+          <t>lama_laba_combination</t>
         </is>
       </c>
       <c r="W266" s="3" t="inlineStr">
         <is>
-          <t>sourcing_boundary</t>
+          <t>issuer_stopped_reporting</t>
         </is>
       </c>
     </row>
